--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -42,21 +42,21 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>115.92</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67.17</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11402</v>
+        <v>11303</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.92</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11303</v>
+        <v>11402</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56.2</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="6">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11203</v>
+        <v>11202</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48.72</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="7">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11202</v>
+        <v>11301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45.43</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11301</v>
+        <v>11203</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>39.04</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.82</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>26.44</v>
+        <v>11.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>51.39</v>
+        <v>513.89</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>36.45</v>
+        <v>364.46</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34.48</v>
+        <v>344.76</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34.17</v>
+        <v>341.74</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23.24</v>
+        <v>232.35</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.53</v>
+        <v>215.35</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.42</v>
+        <v>214.19</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16.59</v>
+        <v>165.94</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.53</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.92</v>
+        <v>119.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:10</t>
+    <t xml:space="preserve">2026-10-04 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:00</t>
+    <t xml:space="preserve">2026-10-05 07:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
